--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2063-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2063-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7D3C285-7847-409C-99AE-024B2356053D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D86AD81C-4E31-4CF7-B026-15A3DD74F570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{93D1046D-716A-47C1-9F36-627AA0FA1501}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{6129ECFF-00AC-40A9-BC5C-CAA8D3640019}"/>
   </bookViews>
   <sheets>
     <sheet name="2063-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1517,20 +1517,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A98A5E91-8BD0-47D6-9616-6553668CC686}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB51277-3A05-4C76-B047-FD797715F2A7}">
   <dimension ref="A1:R48"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1558,7 +1558,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1588,7 +1588,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1684,7 +1684,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>26</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>2024</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>2023</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>26</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2022</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2021</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>26</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>26</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>26</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>26</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2020</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>26</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>26</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>26</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2019</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>2018</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>2017</v>
       </c>
@@ -3624,7 +3624,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>2016</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>4.82</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>2015</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>2014</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39">
         <v>2013</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
         <v>2012</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="39">
         <v>2011</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>5.47</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="37">
         <v>2010</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="39">
         <v>2009</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="37" t="s">
         <v>58</v>
       </c>
